--- a/public/ModeleImportationAchat.xlsx
+++ b/public/ModeleImportationAchat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angelo\Strong Africa\magcarburant\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\magcarburant\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E24061-4EA1-4A47-B35C-664B1C924852}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B596BE-2AB0-44D2-A05A-9E15F4032E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MODELE IMPORT ACHATS" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>PRODUIT</t>
   </si>
@@ -94,6 +97,12 @@
   </si>
   <si>
     <t>ESSENCE | GASOIL | PETROLE | FOMI</t>
+  </si>
+  <si>
+    <t>ZONE</t>
+  </si>
+  <si>
+    <t>NORD | SUD |EST | OUEST</t>
   </si>
 </sst>
 </file>
@@ -213,10 +222,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19F7D991-8B48-4FF8-AFEB-6BB05DB3E7F3}" name="Table2" displayName="Table2" ref="A1:H3000" totalsRowShown="0">
-  <autoFilter ref="A1:H3000" xr:uid="{AF117FD5-8164-4E05-8B07-2900E9EE5898}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19F7D991-8B48-4FF8-AFEB-6BB05DB3E7F3}" name="Table2" displayName="Table2" ref="A1:I3000" totalsRowShown="0">
+  <autoFilter ref="A1:I3000" xr:uid="{AF117FD5-8164-4E05-8B07-2900E9EE5898}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{8D554587-CD84-4BCF-B85E-4BE46737C068}" name="DATE ACHAT"/>
+    <tableColumn id="2" xr3:uid="{0081B4D3-CDEC-478E-A8BD-4DDDEEB21C56}" name="ZONE"/>
     <tableColumn id="3" xr3:uid="{B0AAAA7B-B49B-4213-93C6-F9127F532F52}" name="PRODUIT"/>
     <tableColumn id="4" xr3:uid="{C5EABC09-E73C-47CB-B09B-E1E47D6D0823}" name="FOURNISSEUR"/>
     <tableColumn id="5" xr3:uid="{D932CCAA-A9B2-4899-9FB0-33A8F4DF4C61}" name="NUMERO FACTURE"/>
@@ -230,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FA5846F-6F47-404A-B63D-D6A664F5F8F2}" name="Table3" displayName="Table3" ref="K12:M19" totalsRowShown="0">
-  <autoFilter ref="K12:M19" xr:uid="{E604AD25-C887-4B63-994B-5EA9D7B91566}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FA5846F-6F47-404A-B63D-D6A664F5F8F2}" name="Table3" displayName="Table3" ref="L12:N20" totalsRowShown="0">
+  <autoFilter ref="L12:N20" xr:uid="{E604AD25-C887-4B63-994B-5EA9D7B91566}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{AA7EFDBF-8637-45B5-968C-6EA4D0B830F7}" name="Colonne"/>
     <tableColumn id="2" xr3:uid="{447E7B6C-EDEA-45E5-B1E4-C90D91D49841}" name="Type de données" dataDxfId="1"/>
@@ -504,283 +514,318 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
       <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="K2" s="6" t="s">
+      <c r="B2" s="3"/>
+      <c r="L2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="6"/>
       <c r="M2" s="6"/>
-      <c r="N2" s="4"/>
+      <c r="N2" s="6"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-    </row>
-    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S2" s="4"/>
+    </row>
+    <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="K3" s="6"/>
+      <c r="B3" s="3"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
-      <c r="N3" s="4"/>
+      <c r="N3" s="6"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-    </row>
-    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S3" s="4"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="L4" s="5"/>
+      <c r="B4" s="3"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
-    </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
-      <c r="K5" s="7" t="s">
+      <c r="B5" s="3"/>
+      <c r="L5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="7"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="5"/>
+      <c r="N5" s="7"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
-    </row>
-    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
-      <c r="K6" s="7"/>
+      <c r="B6" s="3"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="5"/>
+      <c r="N6" s="7"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
-      <c r="K7" s="8" t="s">
+      <c r="B7" s="3"/>
+      <c r="L7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="8"/>
       <c r="M7" s="8"/>
-      <c r="N7" s="5"/>
+      <c r="N7" s="8"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="K8" s="8"/>
+      <c r="B8" s="3"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
-      <c r="N8" s="5"/>
+      <c r="N8" s="8"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S8" s="5"/>
+    </row>
+    <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
-      <c r="K9" s="8"/>
+      <c r="B9" s="3"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
-      <c r="N9" s="5"/>
+      <c r="N9" s="8"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
-    </row>
-    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S9" s="5"/>
+    </row>
+    <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
-      <c r="K10" s="8"/>
+      <c r="B10" s="3"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
-      <c r="N10" s="5"/>
+      <c r="N10" s="8"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S10" s="5"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="K12" t="s">
+      <c r="B12" s="3"/>
+      <c r="L12" t="s">
         <v>4</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>5</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="K13" t="s">
+      <c r="B13" s="3"/>
+      <c r="L13" t="s">
         <v>20</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="K14" t="s">
+      <c r="B14" s="3"/>
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="L15" t="s">
         <v>0</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="K15" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="L16" t="s">
         <v>15</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="K16" t="s">
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="L17" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M16" s="1"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="K17" t="s">
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="L18" t="s">
         <v>17</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="K18" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="L19" t="s">
         <v>18</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="K19" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="L20" t="s">
         <v>1</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="1"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="1"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="3"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-    </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
-      <c r="K24" s="9" t="s">
+      <c r="B24" s="3"/>
+      <c r="L24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L24" s="9"/>
       <c r="M24" s="9"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N24" s="9"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
-      <c r="K25" s="9"/>
+      <c r="B25" s="3"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="K2:M3"/>
-    <mergeCell ref="K5:M6"/>
-    <mergeCell ref="K7:M10"/>
-    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="L2:N3"/>
+    <mergeCell ref="L5:N6"/>
+    <mergeCell ref="L7:N10"/>
+    <mergeCell ref="L24:N25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
